--- a/reports/demo/demo_orders_cleaning_report.xlsx
+++ b/reports/demo/demo_orders_cleaning_report.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1217eae69086</t>
+          <t>62ca521e2b51</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:51+00:00</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ff8087c14a0c3c28e42becbbc16c8ca1f145e1683c3c1aac4b4f15d846858d24</t>
+          <t>c7d585b04eea74df1b2e1ac2fa86b71f7fc3a5332c239ab7621b24cb1fe3c291</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>982f3cb742072588b9fd325541ebf2778e5cd56a62ea984c343ef16c0e5aaeff</t>
+          <t>fee5141088b4166788db422727155600bc44407237d913085bff44eaa93b8a26</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2117,13 +2117,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>role=identifier</t>
+          <t>role=identifier, status=ready</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>role=datetime</t>
+          <t>role=datetime, status=review</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>role=datetime</t>
+          <t>role=datetime, status=ready</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>role=text</t>
+          <t>role=text, status=ready</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>role=categorical</t>
+          <t>role=categorical, status=ready</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>role=categorical</t>
+          <t>role=categorical, status=ready</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=review</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=numeric, status=ready</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>role=pii</t>
+          <t>role=pii, status=ready</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>quantity, unit_price, shipping_cost, total</t>
+          <t>unit_price, shipping_cost, total</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>order_date, ship_date</t>
+          <t>ship_date</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>excluded from features</t>
+          <t>needs review before use</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2564,20 +2564,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>order_date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>1 value(s) could not be parsed as datetime64[ns]; column exported as text</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>excluded from features</t>
+          <t>needs review before use</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2587,69 +2591,65 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1 value(s) could not be parsed as Int64; column exported as text</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>excluded from features</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>role=identifier</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>excluded from features</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>pii</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>role=identifier</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2664,17 +2664,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>role=categorical</t>
+          <t>role=identifier, status=ready</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -2691,24 +2691,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>credit_limit</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>role=numeric</t>
+          <t>role=identifier, status=ready</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Int64</t>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>column</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2718,22 +2718,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>region</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>credit_limit</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
+          <t>role=categorical, status=ready</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>feature list</t>
+          <t>column</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2743,22 +2745,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>credit_limit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
+          <t>role=numeric, status=ready</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Int64</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>excluded from features</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2768,65 +2772,115 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>customer_id, name</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>credit_limit</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kept as text</t>
+          <t>feature list (ready)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>intended datetime64[ns]</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1 unparseable</t>
-        </is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>excluded from features</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>customer_id, name</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>kept as text</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>intended datetime64[ns]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1 unparseable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>kept as text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>intended Int64</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>1 unparseable</t>
         </is>
@@ -5808,7 +5862,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5915,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5970,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -5971,7 +6025,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6078,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6131,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6186,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6241,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6296,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-18T06:33:15+00:00</t>
+          <t>2026-10-18T09:13:50+00:00</t>
         </is>
       </c>
     </row>
